--- a/DEV/org.openl.rules.demo/src/org.openl.rules.demo.examples/Example-4-Reference-Guide/rules/7-Functions/BooleanFunctions.xlsx
+++ b/DEV/org.openl.rules.demo/src/org.openl.rules.demo.examples/Example-4-Reference-Guide/rules/7-Functions/BooleanFunctions.xlsx
@@ -548,7 +548,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:I65"/>
+  <dimension ref="B2:I66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.5" customWidth="1" min="1" max="1"/>
@@ -1197,83 +1197,102 @@
     <row r="58">
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>Method Boolean AllAdults(Integer[] ages)</t>
-        </is>
-      </c>
+          <t>Spreadsheet Boolean AllAdults(Integer[] ages)</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="n"/>
     </row>
     <row r="59">
-      <c r="B59" s="6" t="inlineStr">
-        <is>
-          <t>return allTrue(ages[(age) transform to age &gt;= 18]);</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="B61" s="3" t="inlineStr">
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>Step</t>
+        </is>
+      </c>
+      <c r="C59" s="5" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" s="6" t="inlineStr">
+        <is>
+          <t>Result</t>
+        </is>
+      </c>
+      <c r="C60" s="7" t="inlineStr">
+        <is>
+          <t>= allTrue(ages[(age) transform to age &gt;= 18])</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" s="3" t="inlineStr">
         <is>
           <t>Test AllAdults AllAdultsTest</t>
         </is>
       </c>
-      <c r="C61" s="4" t="n"/>
-    </row>
-    <row r="62">
-      <c r="B62" s="9" t="inlineStr">
+      <c r="C62" s="4" t="n"/>
+    </row>
+    <row r="63">
+      <c r="B63" s="9" t="inlineStr">
         <is>
           <t>ages</t>
         </is>
       </c>
-      <c r="C62" s="9" t="inlineStr">
+      <c r="C63" s="9" t="inlineStr">
         <is>
           <t>_res_</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="B63" s="5" t="inlineStr">
+    <row r="64">
+      <c r="B64" s="5" t="inlineStr">
         <is>
           <t>Ages</t>
         </is>
       </c>
-      <c r="C63" s="5" t="inlineStr">
+      <c r="C64" s="5" t="inlineStr">
         <is>
           <t>All Adults</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="B64" s="6" t="inlineStr">
-        <is>
-          <t>20, 35, 18</t>
-        </is>
-      </c>
-      <c r="C64" s="10" t="inlineStr">
-        <is>
-          <t>true</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="B65" s="6" t="inlineStr">
         <is>
+          <t>20, 35, 18</t>
+        </is>
+      </c>
+      <c r="C65" s="10" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" s="6" t="inlineStr">
+        <is>
           <t>20, 17</t>
         </is>
       </c>
-      <c r="C65" s="10" t="inlineStr">
+      <c r="C66" s="10" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
     <mergeCell ref="B56:I56"/>
     <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B62:C62"/>
     <mergeCell ref="B29:C29"/>
     <mergeCell ref="B17:D17"/>
-    <mergeCell ref="B61:C61"/>
     <mergeCell ref="B43:D43"/>
     <mergeCell ref="B27:I27"/>
     <mergeCell ref="B4:I4"/>
+    <mergeCell ref="B58:C58"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
